--- a/gantt_sistema_inventario_emprendedores v1 2.xlsx
+++ b/gantt_sistema_inventario_emprendedores v1 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crfeg\OneDrive - Universidad Libre\Documentos\Universidad Libre\Septimo semestre\Gestion de proyectos\Primer corte\Documentos proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61F54513-128D-409A-8BE5-F9CD543D4746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73E2837E-00BB-4D27-9FAB-1B224750C8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cronograma" sheetId="1" r:id="rId1"/>
@@ -504,7 +504,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,67 +517,57 @@
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1864AB"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF087F5B"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF862E12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF7B4F00"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -713,7 +703,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -726,11 +715,12 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1034,59 +1024,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="32.54296875" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="21" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:21" ht="30" customHeight="1">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1135,13 +1125,13 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+    <row r="3" spans="1:21">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
       <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1188,32 +1178,32 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+    <row r="4" spans="1:21" ht="18" customHeight="1">
+      <c r="A4" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="3" t="s">
         <v>38</v>
       </c>
@@ -1248,32 +1238,32 @@
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
     </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="23" t="s">
+    <row r="6" spans="1:21" ht="18" customHeight="1">
+      <c r="A6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="21"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="21"/>
-      <c r="U6" s="21"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="26"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="26"/>
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="3" t="s">
         <v>44</v>
       </c>
@@ -1308,7 +1298,7 @@
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21">
       <c r="A8" s="9" t="s">
         <v>48</v>
       </c>
@@ -1343,7 +1333,7 @@
       <c r="T8" s="12"/>
       <c r="U8" s="12"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21">
       <c r="A9" s="3" t="s">
         <v>51</v>
       </c>
@@ -1378,7 +1368,7 @@
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21">
       <c r="A10" s="9" t="s">
         <v>53</v>
       </c>
@@ -1413,7 +1403,7 @@
       <c r="T10" s="12"/>
       <c r="U10" s="12"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21">
       <c r="A11" s="3" t="s">
         <v>55</v>
       </c>
@@ -1448,7 +1438,7 @@
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21">
       <c r="A12" s="9" t="s">
         <v>57</v>
       </c>
@@ -1483,7 +1473,7 @@
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21">
       <c r="A13" s="3" t="s">
         <v>60</v>
       </c>
@@ -1518,7 +1508,7 @@
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21">
       <c r="A14" s="3" t="s">
         <v>63</v>
       </c>
@@ -1553,32 +1543,32 @@
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
+    <row r="15" spans="1:21">
+      <c r="A15" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="3" t="s">
         <v>68</v>
       </c>
@@ -1613,7 +1603,7 @@
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21">
       <c r="A17" s="9" t="s">
         <v>72</v>
       </c>
@@ -1648,7 +1638,7 @@
       <c r="T17" s="12"/>
       <c r="U17" s="12"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21">
       <c r="A18" s="3" t="s">
         <v>75</v>
       </c>
@@ -1683,7 +1673,7 @@
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21">
       <c r="A19" s="9" t="s">
         <v>78</v>
       </c>
@@ -1718,7 +1708,7 @@
       <c r="T19" s="12"/>
       <c r="U19" s="12"/>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -1753,7 +1743,7 @@
       <c r="T20" s="7"/>
       <c r="U20" s="7"/>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21">
       <c r="A21" s="9" t="s">
         <v>85</v>
       </c>
@@ -1788,7 +1778,7 @@
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21">
       <c r="A22" s="3" t="s">
         <v>88</v>
       </c>
@@ -1823,7 +1813,7 @@
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21">
       <c r="A23" s="9" t="s">
         <v>91</v>
       </c>
@@ -1858,7 +1848,7 @@
       <c r="T23" s="12"/>
       <c r="U23" s="12"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21">
       <c r="A24" s="3" t="s">
         <v>94</v>
       </c>
@@ -1893,7 +1883,7 @@
       <c r="T24" s="7"/>
       <c r="U24" s="7"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21">
       <c r="A25" s="9" t="s">
         <v>99</v>
       </c>
@@ -1928,7 +1918,7 @@
       <c r="T25" s="12"/>
       <c r="U25" s="12"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21">
       <c r="A26" s="3" t="s">
         <v>101</v>
       </c>
@@ -1963,7 +1953,7 @@
       <c r="T26" s="7"/>
       <c r="U26" s="7"/>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21">
       <c r="A27" s="9" t="s">
         <v>105</v>
       </c>
@@ -1998,7 +1988,7 @@
       <c r="T27" s="12"/>
       <c r="U27" s="12"/>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21">
       <c r="A28" s="3" t="s">
         <v>107</v>
       </c>
@@ -2033,7 +2023,7 @@
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:21">
       <c r="A29" s="9" t="s">
         <v>111</v>
       </c>
@@ -2068,7 +2058,7 @@
       <c r="T29" s="12"/>
       <c r="U29" s="12"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:21">
       <c r="A30" s="3" t="s">
         <v>115</v>
       </c>
@@ -2103,7 +2093,7 @@
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:21">
       <c r="A31" s="9" t="s">
         <v>117</v>
       </c>
@@ -2138,7 +2128,7 @@
       <c r="T31" s="12"/>
       <c r="U31" s="12"/>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21">
       <c r="A32" s="3" t="s">
         <v>120</v>
       </c>
@@ -2173,7 +2163,7 @@
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21">
       <c r="A33" s="9" t="s">
         <v>122</v>
       </c>
@@ -2208,7 +2198,7 @@
       <c r="T33" s="12"/>
       <c r="U33" s="12"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:21">
       <c r="A34" s="3" t="s">
         <v>125</v>
       </c>
@@ -2243,7 +2233,7 @@
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:21">
       <c r="A35" s="9" t="s">
         <v>128</v>
       </c>
@@ -2278,32 +2268,32 @@
       <c r="T35" s="12"/>
       <c r="U35" s="12"/>
     </row>
-    <row r="36" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="28" t="s">
+    <row r="36" spans="1:21" ht="18" customHeight="1">
+      <c r="A36" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="L36" s="21"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
-      <c r="R36" s="21"/>
-      <c r="S36" s="21"/>
-      <c r="T36" s="21"/>
-      <c r="U36" s="21"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="26"/>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" s="3" t="s">
         <v>131</v>
       </c>
@@ -2338,7 +2328,7 @@
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:21">
       <c r="A38" s="9" t="s">
         <v>136</v>
       </c>
@@ -2373,7 +2363,7 @@
       <c r="T38" s="14"/>
       <c r="U38" s="12"/>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:21">
       <c r="A39" s="3" t="s">
         <v>139</v>
       </c>
@@ -2408,7 +2398,7 @@
       <c r="T39" s="14"/>
       <c r="U39" s="14"/>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:21">
       <c r="A40" s="9" t="s">
         <v>141</v>
       </c>
@@ -2443,7 +2433,7 @@
       <c r="T40" s="12"/>
       <c r="U40" s="14"/>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:21">
       <c r="A42" s="15" t="s">
         <v>143</v>
       </c>
@@ -2457,32 +2447,32 @@
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A44" s="26" t="s">
+    <row r="44" spans="1:21">
+      <c r="A44" s="27" t="s">
         <v>147</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="27"/>
-      <c r="N44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="P44" s="27"/>
-      <c r="Q44" s="27"/>
-      <c r="R44" s="27"/>
-      <c r="S44" s="27"/>
-      <c r="T44" s="27"/>
-      <c r="U44" s="27"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28"/>
+      <c r="P44" s="28"/>
+      <c r="Q44" s="28"/>
+      <c r="R44" s="28"/>
+      <c r="S44" s="28"/>
+      <c r="T44" s="28"/>
+      <c r="U44" s="28"/>
+    </row>
+    <row r="45" spans="1:21">
       <c r="A45" s="19" t="s">
         <v>148</v>
       </c>
@@ -2507,7 +2497,7 @@
       <c r="T45" s="19"/>
       <c r="U45" s="19"/>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:21">
       <c r="A46" s="19" t="s">
         <v>149</v>
       </c>
@@ -2532,7 +2522,7 @@
       <c r="T46" s="19"/>
       <c r="U46" s="19"/>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:21">
       <c r="A47" s="19" t="s">
         <v>150</v>
       </c>
@@ -2557,7 +2547,7 @@
       <c r="T47" s="19"/>
       <c r="U47" s="19"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:21">
       <c r="A48" s="19" t="s">
         <v>151</v>
       </c>
@@ -2582,7 +2572,7 @@
       <c r="T48" s="19"/>
       <c r="U48" s="19"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21">
       <c r="A49" s="19" t="s">
         <v>152</v>
       </c>
@@ -2607,7 +2597,7 @@
       <c r="T49" s="19"/>
       <c r="U49" s="19"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:21">
       <c r="A50" s="19" t="s">
         <v>153</v>
       </c>
